--- a/Server/Received_data/Model/Output_1.xlsx
+++ b/Server/Received_data/Model/Output_1.xlsx
@@ -425,16 +425,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>LDA</t>
+          <t>LDA_macro</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Feature</t>
         </is>
@@ -445,9 +450,12 @@
         <v>4</v>
       </c>
       <c r="B2" t="n">
-        <v>0.4117647058823529</v>
-      </c>
-      <c r="C2" t="inlineStr">
+        <v>0.5317460317460317</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.9411764705882353</v>
+      </c>
+      <c r="D2" t="inlineStr">
         <is>
           <t>('Asm_280',)</t>
         </is>
@@ -455,79 +463,145 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>0.3823529411764706</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>('HIX',)</t>
+        <v>0.4991496598639456</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.9411764705882353</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>('FIX',)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.3529411764705883</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>('C_org',)</t>
+        <v>0.444991789819376</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.9411764705882353</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>('Asm_350',)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>0.3529411764705883</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>('FIX',)</t>
+        <v>0.4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.9411764705882353</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>('HIX',)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B6" t="n">
-        <v>0.3235294117647059</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>('Asm_350',)</t>
+        <v>0.2059523809523809</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.9411764705882353</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>('Component_3',)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B7" t="n">
-        <v>0.2941176470588235</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>('E2E3',)</t>
+        <v>0.2059523809523809</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.9411764705882353</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>('Component_1',)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0.2008928571428572</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.9411764705882353</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>('E2E3',)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.1773809523809524</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.9411764705882353</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>('C_org',)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B8" t="n">
-        <v>0.2647058823529412</v>
-      </c>
-      <c r="C8" t="inlineStr">
+      <c r="B10" t="n">
+        <v>0.1470588235294117</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.9411764705882353</v>
+      </c>
+      <c r="D10" t="inlineStr">
         <is>
           <t>('Suva',)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0.1296296296296296</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.9411764705882353</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>('Component_2',)</t>
         </is>
       </c>
     </row>
